--- a/etf_holdings/2026-08-27_common_holdings_all.xlsx
+++ b/etf_holdings/2026-08-27_common_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AM7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,15 +554,60 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>00405A_股票名稱</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>00405A_權重</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>00405A_股數</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>00407A_股票名稱</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>00407A_權重</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>00407A_股數</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>00993A_股票名稱</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>00993A_權重</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>00993A_股數</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
           <t>合計權重</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>平均權重</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>共同持有ETF</t>
         </is>
@@ -580,7 +625,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -589,7 +634,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>9.90%</t>
+          <t>9.87%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -602,7 +647,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11.80%</t>
+          <t>11.74%</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -628,7 +673,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>8.50%</t>
+          <t>8.49%</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -641,7 +686,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>16.87%</t>
+          <t>17.19%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -667,7 +712,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>7.24%</t>
+          <t>7.20%</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -688,17 +733,56 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>79.54%</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>9.94%</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A</t>
+          <t>1.45%</t>
+        </is>
+      </c>
+      <c r="AD2" t="n">
+        <v>179000</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>8.76%</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>991000</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>8.71%</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
+        <v>381000</v>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>98.64%</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>8.97%</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A</t>
         </is>
       </c>
     </row>
@@ -714,7 +798,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -723,11 +807,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>9.85%</t>
+          <t>9.11%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4843000</v>
+        <v>4807000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -736,7 +820,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>9.60%</t>
+          <t>8.93%</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -762,11 +846,11 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>322000</v>
+        <v>319000</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -775,11 +859,11 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>5.23%</t>
         </is>
       </c>
       <c r="R3" t="n">
-        <v>1690000</v>
+        <v>1600000</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -801,7 +885,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>6.29%</t>
+          <t>5.85%</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -822,17 +906,56 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>44.21%</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>5.53%</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A</t>
+          <t>4.20%</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>212000</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>5.80%</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>269000</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>台光電子</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>6.42%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>115000</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>57.94%</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>5.27%</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A</t>
         </is>
       </c>
     </row>
@@ -848,7 +971,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +980,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.01%</t>
+          <t>6.85%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -870,7 +993,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.59%</t>
+          <t>4.48%</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -896,7 +1019,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>6.75%</t>
+          <t>6.62%</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -935,7 +1058,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.35%</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -956,17 +1079,56 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>33.78%</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>4.22%</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A</t>
+          <t>6.36%</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>480000</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>4.63%</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>321000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>3.85%</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>103000</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>48.16%</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>4.38%</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A</t>
         </is>
       </c>
     </row>
@@ -982,7 +1144,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,7 +1153,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4.65%</t>
+          <t>4.73%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1004,7 +1166,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.12%</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -1030,7 +1192,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1043,7 +1205,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="R5" t="n">
@@ -1069,7 +1231,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>5.06%</t>
+          <t>5.13%</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -1090,17 +1252,56 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>24.62%</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3.08%</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A</t>
+          <t>3.65%</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>529000</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2.75%</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>366000</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2.96%</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>152000</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>34.34%</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>3.12%</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1317,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,7 +1326,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>4.29%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1138,7 +1339,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.46%</t>
+          <t>4.88%</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -1173,7 +1374,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>2.03%</t>
         </is>
       </c>
       <c r="R6" t="n">
@@ -1199,7 +1400,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1220,17 +1421,56 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13.66%</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A</t>
+          <t>2.93%</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>739000</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>2.68%</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
+        <v>620000</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2.78%</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
+        <v>249000</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>23.14%</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>2.31%</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1486,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,7 +1495,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3.98%</t>
+          <t>4.06%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1290,11 +1530,11 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>965000</v>
+        <v>956000</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,11 +1543,11 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="R7" t="n">
-        <v>8000000</v>
+        <v>7000000</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1329,7 +1569,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1350,17 +1590,52 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13.30%</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1.90%</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A</t>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>2.46%</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1138000</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>202000</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>16.77%</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>1.86%</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A</t>
         </is>
       </c>
     </row>
